--- a/skills/gara-effort-cost-estimator/assets/template_cost_model.xlsx
+++ b/skills/gara-effort-cost-estimator/assets/template_cost_model.xlsx
@@ -1069,6 +1069,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -2541,6 +2542,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2825,6 +2827,7 @@
       </c>
       <c r="I11" s="34" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
@@ -3069,6 +3072,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -3308,6 +3312,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3500,6 +3505,7 @@
       <c r="F11" s="34" t="n"/>
       <c r="G11" s="34" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
@@ -3548,7 +3554,7 @@
         </is>
       </c>
       <c r="C15" s="49">
-        <f>('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$61/12)*'0. Parametri'!$D$64</f>
+        <f>('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$61/12)*'0. Parametri'!$D$64</f>
         <v/>
       </c>
       <c r="D15" s="57" t="inlineStr"/>
@@ -3568,7 +3574,7 @@
         </is>
       </c>
       <c r="C16" s="49">
-        <f>('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12)</f>
+        <f>('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12)</f>
         <v/>
       </c>
       <c r="D16" s="57" t="inlineStr"/>
@@ -3615,6 +3621,7 @@
       <c r="F18" s="34" t="n"/>
       <c r="G18" s="34" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
@@ -3731,6 +3738,7 @@
       <c r="F25" s="34" t="n"/>
       <c r="G25" s="34" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="59" t="inlineStr">
         <is>
@@ -3798,6 +3806,7 @@
       <c r="F30" s="63" t="n"/>
       <c r="G30" s="63" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="59" t="inlineStr">
         <is>
@@ -3980,6 +3989,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="59" t="inlineStr">
         <is>
@@ -4082,7 +4092,7 @@
         <v/>
       </c>
       <c r="I6" s="45">
-        <f>((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*D6)*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</f>
+        <f>((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*D6)*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</f>
         <v/>
       </c>
       <c r="J6" s="75">
@@ -4128,7 +4138,7 @@
         <v/>
       </c>
       <c r="I7" s="82">
-        <f>((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*D7)*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</f>
+        <f>((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*D7)*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</f>
         <v/>
       </c>
       <c r="J7" s="83">
@@ -4174,7 +4184,7 @@
         <v/>
       </c>
       <c r="I8" s="90">
-        <f>((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*D8)*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</f>
+        <f>((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*D8)*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</f>
         <v/>
       </c>
       <c r="J8" s="91">
@@ -4220,7 +4230,7 @@
         <v/>
       </c>
       <c r="I9" s="49">
-        <f>((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*(('0. Parametri'!$D$9*D9)/('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</f>
+        <f>((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*(('0. Parametri'!$D$9*D9)/('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</f>
         <v/>
       </c>
       <c r="J9" s="97">
@@ -4266,7 +4276,7 @@
         <v/>
       </c>
       <c r="I10" s="49">
-        <f>((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*(('0. Parametri'!$D$9*D10)/('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</f>
+        <f>((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*(('0. Parametri'!$D$9*D10)/('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</f>
         <v/>
       </c>
       <c r="J10" s="97">
@@ -4279,6 +4289,7 @@
       </c>
       <c r="L10" s="99" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="59" t="inlineStr">
         <is>
@@ -4313,23 +4324,23 @@
         <v>0</v>
       </c>
       <c r="B14" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="C14" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="D14" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="E14" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="F14" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.0)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
     </row>
@@ -4338,23 +4349,23 @@
         <v>0.05</v>
       </c>
       <c r="B15" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="C15" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="D15" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="E15" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="F15" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.05)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
     </row>
@@ -4363,23 +4374,23 @@
         <v>0.1</v>
       </c>
       <c r="B16" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="C16" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="D16" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="E16" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="F16" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.1)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
     </row>
@@ -4388,23 +4399,23 @@
         <v>0.15</v>
       </c>
       <c r="B17" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="C17" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="D17" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="E17" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="F17" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.15)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
     </row>
@@ -4413,26 +4424,27 @@
         <v>0.2</v>
       </c>
       <c r="B18" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.0)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="C18" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.05)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="D18" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.08)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="E18" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)</f>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.1)+'0. Parametri'!$D$12)</f>
         <v/>
       </c>
       <c r="F18" s="102">
-        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)</f>
-        <v/>
-      </c>
-    </row>
+        <f>(('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)-((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5)))/('0. Parametri'!$D$7+'0. Parametri'!$D$8*(1-0.2)+(('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12))*(1-0.15)+'0. Parametri'!$D$12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="103" t="inlineStr">
         <is>
@@ -4485,6 +4497,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4747,6 +4760,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="106" t="inlineStr">
         <is>
@@ -4845,6 +4859,8 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="106" t="inlineStr">
         <is>
@@ -4943,6 +4959,8 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="106" t="inlineStr">
         <is>
@@ -5041,6 +5059,8 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="106" t="inlineStr">
         <is>
@@ -5163,6 +5183,8 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="106" t="inlineStr">
         <is>
@@ -5285,6 +5307,8 @@
         </is>
       </c>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="106" t="inlineStr">
         <is>
@@ -5383,6 +5407,8 @@
         </is>
       </c>
     </row>
+    <row r="72"/>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="106" t="inlineStr">
         <is>
@@ -5429,7 +5455,7 @@
       </c>
       <c r="B78" s="109" t="inlineStr">
         <is>
-          <t>↳ =('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12)</t>
+          <t>↳ =('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12)</t>
         </is>
       </c>
     </row>
@@ -5457,6 +5483,8 @@
         </is>
       </c>
     </row>
+    <row r="81"/>
+    <row r="82"/>
     <row r="83">
       <c r="A83" s="106" t="inlineStr">
         <is>
@@ -5575,7 +5603,7 @@
       </c>
       <c r="B93" s="109" t="inlineStr">
         <is>
-          <t>↳ =((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*D7)*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</t>
+          <t>↳ =((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*D7)*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</t>
         </is>
       </c>
     </row>
@@ -5615,6 +5643,7 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" s="108" t="inlineStr">
         <is>
@@ -5719,7 +5748,7 @@
       </c>
       <c r="B106" s="109" t="inlineStr">
         <is>
-          <t>↳ =((('0. Parametri'!$D$30*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*(('0. Parametri'!$D$9*D10)/('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</t>
+          <t>↳ =((('0. Parametri'!$D$24*'0. Parametri'!$D$30+'0. Parametri'!$D$25*'0. Parametri'!$D$31+'0. Parametri'!$D$26*'0. Parametri'!$D$32+'0. Parametri'!$D$27*'0. Parametri'!$D$33+'0. Parametri'!$D$28*'0. Parametri'!$D$34)*'0. Parametri'!$D$60*('0. Parametri'!$D$62/12+'0. Parametri'!$D$61/12*'0. Parametri'!$D$64))+(('0. Parametri'!$D$19*'0. Parametri'!$D$35+'0. Parametri'!$D$20*'0. Parametri'!$D$31+'0. Parametri'!$D$21*'0. Parametri'!$D$33+'0. Parametri'!$D$22*'0. Parametri'!$D$34)*('0. Parametri'!$D$62/12))*(('0. Parametri'!$D$9*D10)/('0. Parametri'!$D$19*'0. Parametri'!$D$14+'0. Parametri'!$D$20*'0. Parametri'!$D$15+'0. Parametri'!$D$21*'0. Parametri'!$D$16+'0. Parametri'!$D$22*'0. Parametri'!$D$17)*('0. Parametri'!$D$62/12)))*(1+('0. Parametri'!$D$70+'0. Parametri'!$D$71+'0. Parametri'!$D$72*1.5))</t>
         </is>
       </c>
     </row>
@@ -5759,6 +5788,8 @@
         </is>
       </c>
     </row>
+    <row r="110"/>
+    <row r="111"/>
     <row r="112">
       <c r="A112" s="106" t="inlineStr">
         <is>
@@ -5869,6 +5900,7 @@
         </is>
       </c>
     </row>
+    <row r="122"/>
     <row r="123">
       <c r="A123" s="108" t="inlineStr">
         <is>
